--- a/mappings/source_to_bronze/us_zip.xlsx
+++ b/mappings/source_to_bronze/us_zip.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nason\Desktop\Projects\ActiveProjects\BlixHealth\mappings\source_to_bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BF0151-EC44-4309-ACBB-82311D8BB937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AEE5B8-BB71-4F07-8CDE-6629ABC515B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38505" yWindow="0" windowWidth="20130" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="43">
   <si>
     <t>source_database</t>
   </si>
@@ -118,6 +118,42 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>us_zips</t>
+  </si>
+  <si>
+    <t>blix_healthcare_db</t>
+  </si>
+  <si>
+    <t>bronze</t>
+  </si>
+  <si>
+    <t>us_zip</t>
+  </si>
+  <si>
+    <t>ingestion_ts</t>
+  </si>
+  <si>
+    <t>strip | to_string</t>
+  </si>
+  <si>
+    <t>strip | to_decimal</t>
+  </si>
+  <si>
+    <t>strip | lower</t>
+  </si>
+  <si>
+    <t>strip | upper</t>
+  </si>
+  <si>
+    <t>strip | to_boolean</t>
+  </si>
+  <si>
+    <t>strip | to_integer</t>
+  </si>
+  <si>
+    <t>strip</t>
   </si>
 </sst>
 </file>
@@ -858,7 +894,7 @@
     <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.21875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.5546875" bestFit="1" customWidth="1"/>
@@ -906,16 +942,28 @@
       <c r="B2" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="5"/>
+      <c r="C2" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>11</v>
+      </c>
       <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="K2" s="6"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
@@ -925,16 +973,28 @@
       <c r="B3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="7"/>
+      <c r="C3" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
+      <c r="E3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="K3" s="8"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -944,16 +1004,28 @@
       <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="E4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
+      <c r="J4" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="K4" s="8"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -963,16 +1035,28 @@
       <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
+      <c r="E5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
+      <c r="J5" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -982,16 +1066,28 @@
       <c r="B6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="7"/>
+      <c r="C6" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="E6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
+      <c r="J6" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1001,16 +1097,28 @@
       <c r="B7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="7"/>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="E7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>16</v>
+      </c>
       <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -1020,16 +1128,28 @@
       <c r="B8" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="7"/>
+      <c r="C8" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
+      <c r="E8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1039,16 +1159,28 @@
       <c r="B9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="7"/>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="E9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -1058,16 +1190,28 @@
       <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
+      <c r="E10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>19</v>
+      </c>
       <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1077,16 +1221,28 @@
       <c r="B11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="7"/>
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+      <c r="E11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="K11" s="8"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -1096,16 +1252,28 @@
       <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="7"/>
+      <c r="C12" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
+      <c r="E12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1115,16 +1283,28 @@
       <c r="B13" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="7"/>
+      <c r="C13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="E13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
+      <c r="J13" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K13" s="8"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1134,14 +1314,24 @@
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="7"/>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D14" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="E14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="8"/>
@@ -1153,16 +1343,28 @@
       <c r="B15" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="7"/>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="E15" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>24</v>
+      </c>
       <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
+      <c r="J15" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="K15" s="8"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1172,16 +1374,28 @@
       <c r="B16" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="7"/>
+      <c r="C16" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D16" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="E16" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
+      <c r="J16" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1191,16 +1405,28 @@
       <c r="B17" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="7"/>
+      <c r="C17" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="E17" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
+      <c r="J17" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="K17" s="8"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
@@ -1210,16 +1436,28 @@
       <c r="B18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="7"/>
+      <c r="C18" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D18" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="E18" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
+      <c r="J18" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="K18" s="8"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -1229,16 +1467,28 @@
       <c r="B19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="7"/>
+      <c r="C19" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="D19" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="E19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>28</v>
+      </c>
       <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
+      <c r="J19" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
@@ -1248,12 +1498,24 @@
       <c r="B20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
+      <c r="C20" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="8"/>

--- a/mappings/source_to_bronze/us_zip.xlsx
+++ b/mappings/source_to_bronze/us_zip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nason\Desktop\Projects\ActiveProjects\BlixHealth\mappings\source_to_bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AEE5B8-BB71-4F07-8CDE-6629ABC515B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB860EE-9196-45EC-AE5B-BD36BD2255C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38505" yWindow="0" windowWidth="20130" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="45">
   <si>
     <t>source_database</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>strip</t>
+  </si>
+  <si>
+    <t>current_timestamp</t>
+  </si>
+  <si>
+    <t>no_transform</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1339,9 @@
         <v>23</v>
       </c>
       <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
+      <c r="J14" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1517,7 +1525,9 @@
         <v>35</v>
       </c>
       <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
+      <c r="J20" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="K20" s="8"/>
     </row>
   </sheetData>

--- a/mappings/source_to_bronze/us_zip.xlsx
+++ b/mappings/source_to_bronze/us_zip.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nason\Desktop\Projects\ActiveProjects\BlixHealth\mappings\source_to_bronze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB860EE-9196-45EC-AE5B-BD36BD2255C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{335CDCF5-1CED-438D-9899-0788E72B6F3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38505" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
